--- a/data/data_labelling/Data_Komentar_KSP_labelling.xlsx
+++ b/data/data_labelling/Data_Komentar_KSP_labelling.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panduan Labeling" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Komentar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referensi" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Panduan Labeling" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data Komentar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Referensi" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
